--- a/v4/03_extracted/SituationChap_PREVISION_ENGAGE_2026.xlsx
+++ b/v4/03_extracted/SituationChap_PREVISION_ENGAGE_2026.xlsx
@@ -1873,7 +1873,7 @@
         <v>134</v>
       </c>
       <c r="L13">
-        <v>-840000</v>
+        <v>0</v>
       </c>
       <c r="M13">
         <v>174213.8</v>
@@ -1882,7 +1882,7 @@
         <v>-1058456</v>
       </c>
       <c r="O13">
-        <v>392669.8</v>
+        <v>1232669.8</v>
       </c>
       <c r="P13">
         <v>1</v>
@@ -1894,10 +1894,10 @@
         <v>232</v>
       </c>
       <c r="S13">
-        <v>-840000</v>
+        <v>0</v>
       </c>
       <c r="T13">
-        <v>-3286494.09</v>
+        <v>0</v>
       </c>
       <c r="U13">
         <v>1606494.09</v>
@@ -2068,7 +2068,7 @@
         <v>137</v>
       </c>
       <c r="L16">
-        <v>-660000</v>
+        <v>0</v>
       </c>
       <c r="M16">
         <v>100291.6</v>
@@ -2077,7 +2077,7 @@
         <v>-839910.4</v>
       </c>
       <c r="O16">
-        <v>280202</v>
+        <v>940202</v>
       </c>
       <c r="P16">
         <v>1</v>
@@ -2089,10 +2089,10 @@
         <v>232</v>
       </c>
       <c r="S16">
-        <v>-660000</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>-2241560.41</v>
+        <v>0</v>
       </c>
       <c r="U16">
         <v>921560.41</v>
@@ -2287,7 +2287,7 @@
         <v>446164.02</v>
       </c>
       <c r="T19">
-        <v>-709072.66</v>
+        <v>0</v>
       </c>
       <c r="U19">
         <v>1601400.69</v>
@@ -2718,7 +2718,7 @@
         <v>147</v>
       </c>
       <c r="L26">
-        <v>-7410000</v>
+        <v>0</v>
       </c>
       <c r="M26">
         <v>0</v>
@@ -2727,7 +2727,7 @@
         <v>-7745806</v>
       </c>
       <c r="O26">
-        <v>335806</v>
+        <v>7745806</v>
       </c>
       <c r="P26">
         <v>1</v>
@@ -2739,10 +2739,10 @@
         <v>232</v>
       </c>
       <c r="S26">
-        <v>-7410000</v>
+        <v>0</v>
       </c>
       <c r="T26">
-        <v>-21407475.96</v>
+        <v>0</v>
       </c>
       <c r="U26">
         <v>6587475.96</v>
@@ -4183,7 +4183,7 @@
         <v>170</v>
       </c>
       <c r="L49">
-        <v>-25000</v>
+        <v>0</v>
       </c>
       <c r="M49">
         <v>1047.6</v>
@@ -4192,7 +4192,7 @@
         <v>-9000</v>
       </c>
       <c r="O49">
-        <v>-14952.4</v>
+        <v>10047.6</v>
       </c>
       <c r="P49">
         <v>0</v>
@@ -4204,10 +4204,10 @@
         <v>232</v>
       </c>
       <c r="S49">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T49">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U49">
         <v>0</v>
@@ -5093,7 +5093,7 @@
         <v>184</v>
       </c>
       <c r="L63">
-        <v>-300000</v>
+        <v>0</v>
       </c>
       <c r="M63">
         <v>3024212.4</v>
@@ -5102,7 +5102,7 @@
         <v>274000</v>
       </c>
       <c r="O63">
-        <v>2450212.4</v>
+        <v>2750212.4</v>
       </c>
       <c r="P63">
         <v>1</v>
@@ -5114,10 +5114,10 @@
         <v>232</v>
       </c>
       <c r="S63">
-        <v>-300000</v>
+        <v>0</v>
       </c>
       <c r="T63">
-        <v>-5451051.67</v>
+        <v>0</v>
       </c>
       <c r="U63">
         <v>4851051.67</v>
@@ -6978,7 +6978,7 @@
         <v>213</v>
       </c>
       <c r="L92">
-        <v>-1560526.4</v>
+        <v>0</v>
       </c>
       <c r="M92">
         <v>138596</v>
@@ -6987,7 +6987,7 @@
         <v>-1225639.1</v>
       </c>
       <c r="O92">
-        <v>-196291.3</v>
+        <v>1364235.1</v>
       </c>
       <c r="P92">
         <v>1</v>
@@ -6999,10 +6999,10 @@
         <v>232</v>
       </c>
       <c r="S92">
-        <v>-1560526.4</v>
+        <v>0</v>
       </c>
       <c r="T92">
-        <v>-3814540.72</v>
+        <v>0</v>
       </c>
       <c r="U92">
         <v>693487.92</v>
@@ -7238,7 +7238,7 @@
         <v>217</v>
       </c>
       <c r="L96">
-        <v>-250000</v>
+        <v>0</v>
       </c>
       <c r="M96">
         <v>-977039.5</v>
@@ -7247,7 +7247,7 @@
         <v>-34000</v>
       </c>
       <c r="O96">
-        <v>-1193039.5</v>
+        <v>-943039.5</v>
       </c>
       <c r="R96" t="s">
         <v>231</v>
@@ -7583,7 +7583,7 @@
         <v>223</v>
       </c>
       <c r="L102">
-        <v>-1293346.8</v>
+        <v>0</v>
       </c>
       <c r="M102">
         <v>-4583756.4</v>
@@ -7592,7 +7592,7 @@
         <v>-147982.8</v>
       </c>
       <c r="O102">
-        <v>-5729120.4</v>
+        <v>-4435773.6</v>
       </c>
       <c r="P102">
         <v>0</v>
@@ -7604,10 +7604,10 @@
         <v>232</v>
       </c>
       <c r="S102">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T102">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U102">
         <v>0</v>
@@ -7672,7 +7672,7 @@
         <v>7040000</v>
       </c>
       <c r="T103">
-        <v>-975984.03</v>
+        <v>0</v>
       </c>
       <c r="U103">
         <v>15055984.03</v>
@@ -7778,7 +7778,7 @@
         <v>226</v>
       </c>
       <c r="L105">
-        <v>-298000</v>
+        <v>0</v>
       </c>
       <c r="M105">
         <v>999569.4</v>
@@ -7787,7 +7787,7 @@
         <v>-56691.2</v>
       </c>
       <c r="O105">
-        <v>758260.6</v>
+        <v>1056260.6</v>
       </c>
       <c r="R105" t="s">
         <v>231</v>
